--- a/completed/PDI_synthesis_10.1002.ange.201913625.xlsx
+++ b/completed/PDI_synthesis_10.1002.ange.201913625.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/core/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/completed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D81FB15-0388-8540-858D-9018ABF474AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08173F6-9820-6D48-99CE-D4F1A5C796A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7700" yWindow="500" windowWidth="28140" windowHeight="21900" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="86">
   <si>
     <t>REACTION</t>
   </si>
@@ -972,6 +972,10 @@
       <c r="G15" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="H15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="1" t="s">
@@ -980,6 +984,12 @@
       <c r="E16" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="H16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
@@ -999,6 +1009,12 @@
       </c>
       <c r="G17" s="1" t="s">
         <v>73</v>
+      </c>
+      <c r="H17" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
